--- a/data_sources/Relocation_WindFarms.xlsx
+++ b/data_sources/Relocation_WindFarms.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomsc\.julia\dev\EU_grid_operations_thesis\data_sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF308256-F31C-446D-AD3A-0495C6441B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE6A6F8-EDFD-4820-9783-9ED77AEE8057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{BCA74855-F4A1-4BF0-92B2-3FF72AB887F5}"/>
+    <workbookView minimized="1" xWindow="30630" yWindow="1830" windowWidth="21600" windowHeight="11235" xr2:uid="{BCA74855-F4A1-4BF0-92B2-3FF72AB887F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="Blad2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="90">
   <si>
     <t>WindFarm</t>
   </si>
@@ -279,6 +280,33 @@
   </si>
   <si>
     <t>dc_Bus</t>
+  </si>
+  <si>
+    <t>DC_bus</t>
+  </si>
+  <si>
+    <t>OFF1</t>
+  </si>
+  <si>
+    <t>OFF2</t>
+  </si>
+  <si>
+    <t>OFF3</t>
+  </si>
+  <si>
+    <t>OFF4</t>
+  </si>
+  <si>
+    <t>OFF5</t>
+  </si>
+  <si>
+    <t>Kolom1</t>
+  </si>
+  <si>
+    <t>Offshore_Hub</t>
+  </si>
+  <si>
+    <t>Already_connected</t>
   </si>
 </sst>
 </file>
@@ -320,7 +348,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -340,17 +368,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -378,12 +395,20 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
@@ -426,23 +451,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9272E8ED-FA61-49ED-A95B-0D698D188433}" name="Tabel1" displayName="Tabel1" ref="A1:K97" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:K97" xr:uid="{9272E8ED-FA61-49ED-A95B-0D698D188433}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E97">
-    <sortCondition ref="B1:B97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9272E8ED-FA61-49ED-A95B-0D698D188433}" name="Tabel1" displayName="Tabel1" ref="A1:M97" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:M97" xr:uid="{9272E8ED-FA61-49ED-A95B-0D698D188433}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M97">
+    <sortCondition ref="A1:A97"/>
   </sortState>
-  <tableColumns count="11">
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{ECD423D0-C035-42C3-B14B-1981A64C18BA}" name="WindFarm"/>
     <tableColumn id="2" xr3:uid="{8AEA25C8-934C-42E4-98FC-1E5ED953108D}" name="zone"/>
     <tableColumn id="3" xr3:uid="{86618B0D-2083-4A3B-ADFE-3BB85006A8D2}" name="old_index"/>
     <tableColumn id="4" xr3:uid="{B08B3DDF-806F-4390-89F9-D25ABB306C94}" name="old_lat"/>
     <tableColumn id="5" xr3:uid="{E7E9B36F-94F1-48A5-BDA3-60DAD541FC74}" name="old_lon"/>
-    <tableColumn id="6" xr3:uid="{53B38EA1-2AEC-4D35-92C8-FDE16E7FFF7C}" name="p_max" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{53B38EA1-2AEC-4D35-92C8-FDE16E7FFF7C}" name="p_max" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{1314661E-BE3A-4C59-BE7B-CC32E8D927E5}" name="dc_Bus"/>
     <tableColumn id="9" xr3:uid="{3B321004-87F2-4827-83F4-AD5C8151105A}" name="index"/>
-    <tableColumn id="10" xr3:uid="{D27A49C6-16DB-474E-A38C-275BD785F1DC}" name="lat" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{8EA95326-A829-4289-85E8-0A80F09F84AA}" name="lon" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{D27A49C6-16DB-474E-A38C-275BD785F1DC}" name="lat" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{8EA95326-A829-4289-85E8-0A80F09F84AA}" name="lon" dataDxfId="2"/>
     <tableColumn id="13" xr3:uid="{FF38BEE9-812B-4546-94A9-B8D7F747DBB4}" name="name"/>
+    <tableColumn id="7" xr3:uid="{C1A6A572-9C3E-4CEB-90A7-39076E7AC457}" name="Kolom1"/>
+    <tableColumn id="12" xr3:uid="{D983D19C-7C20-400E-8AC5-9C9BD4E5848F}" name="Already_connected"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8730F81F-4895-464B-B121-34DAE892DDBB}" name="Tabel2" displayName="Tabel2" ref="A1:E6" totalsRowShown="0">
+  <autoFilter ref="A1:E6" xr:uid="{8730F81F-4895-464B-B121-34DAE892DDBB}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{6A7B470A-2DB5-46CF-9C70-EC72C6DEC69F}" name="Offshore_Hub"/>
+    <tableColumn id="2" xr3:uid="{744B8BB2-6C9B-4DE0-8223-A570790EB5CB}" name="lat" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{E33DEB67-5A6B-4CF2-B58F-C45BBD8C73EC}" name="lon" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{70D0DAE2-3013-49E2-814F-1C9703064AA8}" name="DC_bus"/>
+    <tableColumn id="5" xr3:uid="{FF76D31F-2C00-49C0-AEBB-1C85CDBFE4BF}" name="zone"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -816,6 +857,12 @@
       <c r="K1" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
@@ -834,7 +881,7 @@
         <v>4.0296564579999998</v>
       </c>
       <c r="F2" s="4">
-        <v>931.95649456182002</v>
+        <v>931.96</v>
       </c>
       <c r="G2">
         <v>30000</v>
@@ -843,412 +890,444 @@
         <v>20000</v>
       </c>
       <c r="I2" s="6">
-        <v>51.5351127333333</v>
+        <v>51.5351</v>
       </c>
       <c r="J2" s="6">
-        <v>2.4925608499999998</v>
+        <v>2.4925999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3925</v>
+        <v>3923</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D3">
-        <v>51.083296779999998</v>
+        <v>51.267189430000002</v>
       </c>
       <c r="E3">
-        <v>3.0815170940000001</v>
+        <v>3.2085445880000001</v>
       </c>
       <c r="F3" s="4">
-        <v>367.13474445017999</v>
+        <v>914.78</v>
       </c>
       <c r="G3">
-        <v>30001</v>
+        <v>30003</v>
       </c>
       <c r="H3">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="I3" s="6">
-        <v>51.527777999999998</v>
+        <v>51.551699999999997</v>
       </c>
       <c r="J3" s="6">
-        <v>3.0319440000000002</v>
+        <v>2.9668999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3926</v>
+        <v>3924</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D4">
-        <v>51.054157230000001</v>
+        <v>51.210899439999999</v>
       </c>
       <c r="E4">
-        <v>3.6309446059999999</v>
+        <v>3.75426993</v>
       </c>
       <c r="F4" s="4">
-        <v>1528.26</v>
+        <v>300.81</v>
       </c>
       <c r="G4">
-        <v>30002</v>
+        <v>30004</v>
       </c>
       <c r="H4">
-        <v>20002</v>
+        <v>20004</v>
       </c>
       <c r="I4" s="6">
-        <v>51.5617968166666</v>
+        <v>51.72</v>
       </c>
       <c r="J4" s="6">
-        <v>2.5765168150000002</v>
+        <v>2.7357999999999998</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3923</v>
+        <v>3925</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D5">
-        <v>51.267189430000002</v>
+        <v>51.083296779999998</v>
       </c>
       <c r="E5">
-        <v>3.2085445880000001</v>
+        <v>3.0815170940000001</v>
       </c>
       <c r="F5" s="4">
-        <v>914.77912651733197</v>
+        <v>367.13</v>
       </c>
       <c r="G5">
-        <v>30003</v>
+        <v>30001</v>
       </c>
       <c r="H5">
-        <v>20003</v>
+        <v>20001</v>
       </c>
       <c r="I5" s="6">
-        <v>51.551667000000002</v>
+        <v>51.527799999999999</v>
       </c>
       <c r="J5" s="6">
-        <v>2.9669439999999998</v>
-      </c>
-      <c r="M5" s="9"/>
+        <v>3.0318999999999998</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>3924</v>
+        <v>3926</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D6">
-        <v>51.210899439999999</v>
+        <v>51.054157230000001</v>
       </c>
       <c r="E6">
-        <v>3.75426993</v>
+        <v>3.6309446059999999</v>
       </c>
       <c r="F6" s="4">
-        <v>300.81362932369598</v>
+        <v>1528.26</v>
       </c>
       <c r="G6">
-        <v>30004</v>
+        <v>30002</v>
       </c>
       <c r="H6">
-        <v>20004</v>
+        <v>20002</v>
       </c>
       <c r="I6" s="6">
-        <v>51.72</v>
+        <v>51.561799999999998</v>
       </c>
       <c r="J6" s="6">
-        <v>2.735833</v>
+        <v>2.5764999999999998</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>3935</v>
+        <v>3927</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="D7">
-        <v>54.35</v>
+        <v>54.947000000000003</v>
       </c>
       <c r="E7">
-        <v>6.7830000000000004</v>
+        <v>7.5919999999999996</v>
       </c>
       <c r="F7" s="4">
-        <v>348.24</v>
+        <v>438.97</v>
       </c>
       <c r="G7">
-        <v>30005</v>
+        <v>30020</v>
       </c>
       <c r="H7">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="I7" s="6">
-        <v>54.35</v>
+        <v>54.947000000000003</v>
       </c>
       <c r="J7" s="6">
-        <v>6.7830000000000004</v>
+        <v>7.5919999999999996</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>3930</v>
+        <v>3928</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D8">
-        <v>54.35</v>
+        <v>54.5</v>
       </c>
       <c r="E8">
-        <v>6.7830000000000004</v>
+        <v>7.1180000000000003</v>
       </c>
       <c r="F8" s="4">
-        <v>260.65658207275902</v>
+        <v>3548.72</v>
       </c>
       <c r="G8">
-        <v>30006</v>
+        <v>30016</v>
       </c>
       <c r="H8">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="I8" s="6">
-        <v>54.35</v>
+        <v>54.5</v>
       </c>
       <c r="J8" s="6">
-        <v>6.7830000000000004</v>
+        <v>7.1180000000000003</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>3937</v>
+        <v>3929</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="D9">
-        <v>54.25</v>
+        <v>54.371000000000002</v>
       </c>
       <c r="E9">
-        <v>6.7779999999999996</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="F9" s="4">
-        <v>215.54362416107301</v>
+        <v>275.94</v>
       </c>
       <c r="G9">
-        <v>30007</v>
+        <v>30030</v>
       </c>
       <c r="H9">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="I9" s="6">
-        <v>54.25</v>
+        <v>54.371000000000002</v>
       </c>
       <c r="J9" s="6">
-        <v>6.7779999999999996</v>
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>3939</v>
+        <v>3930</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>533</v>
+        <v>479</v>
       </c>
       <c r="D10">
-        <v>54.01</v>
+        <v>54.35</v>
       </c>
       <c r="E10">
-        <v>7.1559999999999997</v>
+        <v>6.7830000000000004</v>
       </c>
       <c r="F10" s="4">
-        <v>301.42967870983802</v>
+        <v>260.66000000000003</v>
       </c>
       <c r="G10">
-        <v>30008</v>
+        <v>30006</v>
       </c>
       <c r="H10">
-        <v>533</v>
+        <v>479</v>
       </c>
       <c r="I10" s="6">
-        <v>54.01</v>
+        <v>54.35</v>
       </c>
       <c r="J10" s="6">
-        <v>7.1559999999999997</v>
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>3950</v>
+        <v>3931</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>529</v>
+        <v>480</v>
       </c>
       <c r="D11">
-        <v>54.01887</v>
+        <v>54.35</v>
       </c>
       <c r="E11">
-        <v>10.06227</v>
+        <v>6.7830000000000004</v>
       </c>
       <c r="F11" s="4">
-        <v>2379.40142517814</v>
+        <v>2385.23</v>
       </c>
       <c r="G11">
-        <v>30009</v>
+        <v>30013</v>
       </c>
       <c r="H11">
-        <v>20005</v>
+        <v>480</v>
       </c>
       <c r="I11" s="6">
-        <v>54.905999999999999</v>
+        <v>54.35</v>
       </c>
       <c r="J11" s="6">
-        <v>6.3150000000000004</v>
-      </c>
-      <c r="K11" t="s">
-        <v>16</v>
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>3944</v>
+        <v>3932</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>743</v>
+        <v>481</v>
       </c>
       <c r="D12">
-        <v>52.936047000000002</v>
+        <v>54.35</v>
       </c>
       <c r="E12">
-        <v>7.1669749999999999</v>
+        <v>6.7830000000000004</v>
       </c>
       <c r="F12" s="4">
-        <v>1632.38004750593</v>
+        <v>2117.98</v>
       </c>
       <c r="G12">
-        <v>30010</v>
+        <v>30021</v>
       </c>
       <c r="H12">
-        <v>20006</v>
+        <v>481</v>
       </c>
       <c r="I12" s="6">
-        <v>54.067888889999999</v>
+        <v>54.35</v>
       </c>
       <c r="J12" s="6">
-        <v>6.17188889</v>
-      </c>
-      <c r="K12" t="s">
-        <v>17</v>
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>3943</v>
+        <v>3933</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13">
-        <v>594</v>
+        <v>482</v>
       </c>
       <c r="D13">
-        <v>53.8</v>
+        <v>54.35</v>
       </c>
       <c r="E13">
-        <v>6.7169999999999996</v>
+        <v>6.7830000000000004</v>
       </c>
       <c r="F13" s="4">
-        <v>387.43586534851698</v>
+        <v>1138.6300000000001</v>
       </c>
       <c r="G13">
-        <v>30011</v>
+        <v>30023</v>
       </c>
       <c r="H13">
-        <v>594</v>
+        <v>482</v>
       </c>
       <c r="I13" s="6">
-        <v>53.8</v>
+        <v>54.35</v>
       </c>
       <c r="J13" s="6">
-        <v>6.7169999999999996</v>
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>3941</v>
+        <v>3934</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14">
-        <v>566</v>
+        <v>483</v>
       </c>
       <c r="D14">
-        <v>53.89</v>
+        <v>54.35</v>
       </c>
       <c r="E14">
-        <v>6.78</v>
+        <v>6.7830000000000004</v>
       </c>
       <c r="F14" s="4">
-        <v>1844.6252033537701</v>
+        <v>1541.13</v>
       </c>
       <c r="G14">
-        <v>30012</v>
+        <v>30019</v>
       </c>
       <c r="H14">
-        <v>566</v>
+        <v>483</v>
       </c>
       <c r="I14" s="6">
-        <v>53.89</v>
+        <v>54.35</v>
       </c>
       <c r="J14" s="6">
-        <v>6.78</v>
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>3931</v>
+        <v>3935</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D15">
         <v>54.35</v>
@@ -1257,13 +1336,13 @@
         <v>6.7830000000000004</v>
       </c>
       <c r="F15" s="4">
-        <v>2385.22615326915</v>
+        <v>348.24</v>
       </c>
       <c r="G15">
-        <v>30013</v>
+        <v>30005</v>
       </c>
       <c r="H15">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I15" s="6">
         <v>54.35</v>
@@ -1271,421 +1350,463 @@
       <c r="J15" s="6">
         <v>6.7830000000000004</v>
       </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>3951</v>
+        <v>3936</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>536</v>
+        <v>485</v>
       </c>
       <c r="D16">
-        <v>54.007336000000002</v>
+        <v>54.35</v>
       </c>
       <c r="E16">
-        <v>10.099728000000001</v>
+        <v>6.7830000000000004</v>
       </c>
       <c r="F16" s="4">
-        <v>2581.82955825303</v>
+        <v>354.11</v>
       </c>
       <c r="G16">
-        <v>30014</v>
+        <v>30022</v>
       </c>
       <c r="H16">
-        <v>20007</v>
+        <v>485</v>
       </c>
       <c r="I16" s="6">
-        <v>54.905999999999999</v>
+        <v>54.35</v>
       </c>
       <c r="J16" s="6">
-        <v>6.3150000000000004</v>
-      </c>
-      <c r="K16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>3942</v>
+        <v>3937</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>567</v>
+        <v>492</v>
       </c>
       <c r="D17">
-        <v>53.89</v>
+        <v>54.25</v>
       </c>
       <c r="E17">
-        <v>6.78</v>
+        <v>6.7779999999999996</v>
       </c>
       <c r="F17" s="4">
-        <v>397.53769221152601</v>
+        <v>215.54</v>
       </c>
       <c r="G17">
-        <v>30015</v>
+        <v>30007</v>
       </c>
       <c r="H17">
-        <v>567</v>
+        <v>492</v>
       </c>
       <c r="I17" s="6">
-        <v>53.89</v>
+        <v>54.25</v>
       </c>
       <c r="J17" s="6">
-        <v>6.78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.7779999999999996</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>3928</v>
+        <v>3938</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="D18">
-        <v>54.5</v>
+        <v>54.207999999999998</v>
       </c>
       <c r="E18">
-        <v>7.1180000000000003</v>
+        <v>8.0220000000000002</v>
       </c>
       <c r="F18" s="4">
-        <v>3548.71558944868</v>
+        <v>270.85000000000002</v>
       </c>
       <c r="G18">
-        <v>30016</v>
+        <v>30024</v>
       </c>
       <c r="H18">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="I18" s="6">
-        <v>54.5</v>
+        <v>54.207999999999998</v>
       </c>
       <c r="J18" s="6">
-        <v>7.1180000000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.0220000000000002</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>3946</v>
+        <v>3939</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>466</v>
+        <v>533</v>
       </c>
       <c r="D19">
-        <v>54.567999999999998</v>
+        <v>54.01</v>
       </c>
       <c r="E19">
-        <v>14.045</v>
+        <v>7.1559999999999997</v>
       </c>
       <c r="F19" s="4">
-        <v>787.78625954198401</v>
+        <v>301.43</v>
       </c>
       <c r="G19">
-        <v>30017</v>
+        <v>30008</v>
       </c>
       <c r="H19">
-        <v>466</v>
+        <v>533</v>
       </c>
       <c r="I19" s="6">
-        <v>54.567999999999998</v>
+        <v>54.01</v>
       </c>
       <c r="J19" s="6">
-        <v>14.045</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.1559999999999997</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>3953</v>
+        <v>3940</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D20">
-        <v>53.990875000000003</v>
+        <v>54.01</v>
       </c>
       <c r="E20">
-        <v>13.252065999999999</v>
+        <v>7.1559999999999997</v>
       </c>
       <c r="F20" s="4">
-        <v>220.28084667010799</v>
+        <v>1657.36</v>
       </c>
       <c r="G20">
-        <v>30018</v>
+        <v>30025</v>
       </c>
       <c r="H20">
-        <v>20008</v>
+        <v>534</v>
       </c>
       <c r="I20" s="6">
-        <v>54.820972230000002</v>
+        <v>54.01</v>
       </c>
       <c r="J20" s="6">
-        <v>13.64797222</v>
-      </c>
-      <c r="K20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.1559999999999997</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>3934</v>
+        <v>3941</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>483</v>
+        <v>566</v>
       </c>
       <c r="D21">
-        <v>54.35</v>
+        <v>53.89</v>
       </c>
       <c r="E21">
-        <v>6.7830000000000004</v>
+        <v>6.78</v>
       </c>
       <c r="F21" s="4">
-        <v>1541.13377549743</v>
+        <v>1844.63</v>
       </c>
       <c r="G21">
-        <v>30019</v>
+        <v>30012</v>
       </c>
       <c r="H21">
-        <v>483</v>
+        <v>566</v>
       </c>
       <c r="I21" s="6">
-        <v>54.35</v>
+        <v>53.89</v>
       </c>
       <c r="J21" s="6">
-        <v>6.7830000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.78</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>3927</v>
+        <v>3942</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22">
-        <v>457</v>
+        <v>567</v>
       </c>
       <c r="D22">
-        <v>54.947000000000003</v>
+        <v>53.89</v>
       </c>
       <c r="E22">
-        <v>7.5919999999999996</v>
+        <v>6.78</v>
       </c>
       <c r="F22" s="4">
-        <v>438.96615208206799</v>
+        <v>397.54</v>
       </c>
       <c r="G22">
-        <v>30020</v>
+        <v>30015</v>
       </c>
       <c r="H22">
-        <v>457</v>
+        <v>567</v>
       </c>
       <c r="I22" s="6">
-        <v>54.947000000000003</v>
+        <v>53.89</v>
       </c>
       <c r="J22" s="6">
-        <v>7.5919999999999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.78</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>3932</v>
+        <v>3943</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23">
-        <v>481</v>
+        <v>594</v>
       </c>
       <c r="D23">
-        <v>54.35</v>
+        <v>53.8</v>
       </c>
       <c r="E23">
-        <v>6.7830000000000004</v>
+        <v>6.7169999999999996</v>
       </c>
       <c r="F23" s="4">
-        <v>2117.98273057189</v>
+        <v>387.44</v>
       </c>
       <c r="G23">
-        <v>30021</v>
+        <v>30011</v>
       </c>
       <c r="H23">
-        <v>481</v>
+        <v>594</v>
       </c>
       <c r="I23" s="6">
-        <v>54.35</v>
+        <v>53.8</v>
       </c>
       <c r="J23" s="6">
-        <v>6.7830000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.7169999999999996</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>3936</v>
+        <v>3944</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24">
-        <v>485</v>
+        <v>743</v>
       </c>
       <c r="D24">
-        <v>54.35</v>
+        <v>52.936047000000002</v>
       </c>
       <c r="E24">
-        <v>6.7830000000000004</v>
+        <v>7.1669749999999999</v>
       </c>
       <c r="F24" s="4">
-        <v>354.10738255033499</v>
+        <v>1632.38</v>
       </c>
       <c r="G24">
-        <v>30022</v>
+        <v>30010</v>
       </c>
       <c r="H24">
-        <v>485</v>
+        <v>20006</v>
       </c>
       <c r="I24" s="6">
-        <v>54.35</v>
+        <v>54.067900000000002</v>
       </c>
       <c r="J24" s="6">
-        <v>6.7830000000000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.1718999999999999</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>3933</v>
+        <v>3945</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>482</v>
+        <v>747</v>
       </c>
       <c r="D25">
-        <v>54.35</v>
+        <v>52.906086000000002</v>
       </c>
       <c r="E25">
-        <v>6.7830000000000004</v>
+        <v>7.1465854999999996</v>
       </c>
       <c r="F25" s="4">
-        <v>1138.6309598298001</v>
+        <v>429.57</v>
       </c>
       <c r="G25">
-        <v>30023</v>
+        <v>30031</v>
       </c>
       <c r="H25">
-        <v>482</v>
+        <v>20013</v>
       </c>
       <c r="I25" s="6">
-        <v>54.35</v>
+        <v>54.067900000000002</v>
       </c>
       <c r="J25" s="6">
-        <v>6.7830000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.1718999999999999</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>3938</v>
+        <v>3946</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26">
-        <v>497</v>
+        <v>466</v>
       </c>
       <c r="D26">
-        <v>54.207999999999998</v>
+        <v>54.567999999999998</v>
       </c>
       <c r="E26">
-        <v>8.0220000000000002</v>
+        <v>14.045</v>
       </c>
       <c r="F26" s="4">
-        <v>270.84985623202903</v>
+        <v>787.79</v>
       </c>
       <c r="G26">
-        <v>30024</v>
+        <v>30017</v>
       </c>
       <c r="H26">
-        <v>497</v>
+        <v>466</v>
       </c>
       <c r="I26" s="6">
-        <v>54.207999999999998</v>
+        <v>54.567999999999998</v>
       </c>
       <c r="J26" s="6">
-        <v>8.0220000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14.045</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>3940</v>
+        <v>3947</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>534</v>
+        <v>627</v>
       </c>
       <c r="D27">
-        <v>54.01</v>
+        <v>54.403804999999998</v>
       </c>
       <c r="E27">
-        <v>7.1559999999999997</v>
+        <v>13.840249</v>
       </c>
       <c r="F27" s="4">
-        <v>1657.36453510198</v>
+        <v>645.73</v>
       </c>
       <c r="G27">
-        <v>30025</v>
+        <v>30029</v>
       </c>
       <c r="H27">
-        <v>534</v>
+        <v>20012</v>
       </c>
       <c r="I27" s="6">
-        <v>54.01</v>
+        <v>54.905999999999999</v>
       </c>
       <c r="J27" s="6">
-        <v>7.1559999999999997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.3150000000000004</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>494</v>
+        <v>627</v>
       </c>
       <c r="D28">
-        <v>54.241917000000001</v>
+        <v>54.345215000000003</v>
       </c>
       <c r="E28">
-        <v>13.648303</v>
+        <v>13.750363</v>
       </c>
       <c r="F28" s="4">
-        <v>1291.4528844950501</v>
+        <v>215.54</v>
       </c>
       <c r="G28">
-        <v>30026</v>
+        <v>30028</v>
       </c>
       <c r="H28">
-        <v>20009</v>
+        <v>20011</v>
       </c>
       <c r="I28" s="6">
         <v>54.905999999999999</v>
@@ -1696,31 +1817,34 @@
       <c r="K28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>3952</v>
+        <v>3949</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>537</v>
+        <v>627</v>
       </c>
       <c r="D29">
-        <v>53.991570000000003</v>
+        <v>54.241917000000001</v>
       </c>
       <c r="E29">
-        <v>10.044302</v>
+        <v>13.648303</v>
       </c>
       <c r="F29" s="4">
-        <v>1201.0511825804001</v>
+        <v>1291.45</v>
       </c>
       <c r="G29">
-        <v>30027</v>
+        <v>30026</v>
       </c>
       <c r="H29">
-        <v>20010</v>
+        <v>20009</v>
       </c>
       <c r="I29" s="6">
         <v>54.905999999999999</v>
@@ -1731,31 +1855,34 @@
       <c r="K29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>3948</v>
+        <v>3950</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="D30">
-        <v>54.345215000000003</v>
+        <v>54.01887</v>
       </c>
       <c r="E30">
-        <v>13.750363</v>
+        <v>10.06227</v>
       </c>
       <c r="F30" s="4">
-        <v>215.54362416107301</v>
+        <v>2379.4</v>
       </c>
       <c r="G30">
-        <v>30028</v>
+        <v>30009</v>
       </c>
       <c r="H30">
-        <v>20011</v>
+        <v>20005</v>
       </c>
       <c r="I30" s="6">
         <v>54.905999999999999</v>
@@ -1766,31 +1893,34 @@
       <c r="K30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>3947</v>
+        <v>3951</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>476</v>
+        <v>536</v>
       </c>
       <c r="D31">
-        <v>54.403804999999998</v>
+        <v>54.007336000000002</v>
       </c>
       <c r="E31">
-        <v>13.840249</v>
+        <v>10.099728000000001</v>
       </c>
       <c r="F31" s="4">
-        <v>645.72644224752798</v>
+        <v>2581.83</v>
       </c>
       <c r="G31">
-        <v>30029</v>
+        <v>30014</v>
       </c>
       <c r="H31">
-        <v>20012</v>
+        <v>20007</v>
       </c>
       <c r="I31" s="6">
         <v>54.905999999999999</v>
@@ -1801,215 +1931,239 @@
       <c r="K31" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>3929</v>
+        <v>3952</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>477</v>
+        <v>537</v>
       </c>
       <c r="D32">
-        <v>54.371000000000002</v>
+        <v>53.991570000000003</v>
       </c>
       <c r="E32">
-        <v>8.0399999999999991</v>
+        <v>10.044302</v>
       </c>
       <c r="F32" s="4">
-        <v>275.94321115126399</v>
+        <v>1201.05</v>
       </c>
       <c r="G32">
-        <v>30030</v>
+        <v>30027</v>
       </c>
       <c r="H32">
-        <v>477</v>
+        <v>20010</v>
       </c>
       <c r="I32" s="6">
-        <v>54.371000000000002</v>
+        <v>54.905999999999999</v>
       </c>
       <c r="J32" s="6">
-        <v>8.0399999999999991</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>6.3150000000000004</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>3945</v>
+        <v>3953</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>747</v>
+        <v>538</v>
       </c>
       <c r="D33">
-        <v>52.906086000000002</v>
+        <v>53.990875000000003</v>
       </c>
       <c r="E33">
-        <v>7.1465854999999996</v>
+        <v>13.252065999999999</v>
       </c>
       <c r="F33" s="4">
-        <v>429.57369671208897</v>
+        <v>220.28</v>
       </c>
       <c r="G33">
-        <v>30031</v>
+        <v>30018</v>
       </c>
       <c r="H33">
-        <v>20013</v>
+        <v>20008</v>
       </c>
       <c r="I33" s="6">
-        <v>54.067888889999999</v>
+        <v>54.820999999999998</v>
       </c>
       <c r="J33" s="6">
-        <v>6.17188889</v>
+        <v>13.648</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>1494</v>
+        <v>1434</v>
       </c>
       <c r="D34">
-        <v>55.524000000000001</v>
+        <v>57.098133580000002</v>
       </c>
       <c r="E34">
-        <v>8.7149999999999999</v>
+        <v>10.03014217</v>
       </c>
       <c r="F34" s="4">
-        <v>64.572644224752807</v>
+        <v>233.31</v>
       </c>
       <c r="G34">
-        <v>30032</v>
+        <v>30037</v>
       </c>
       <c r="H34">
-        <v>20014</v>
+        <v>20019</v>
       </c>
       <c r="I34" s="6">
-        <v>55.485972220000001</v>
+        <v>57.55</v>
       </c>
       <c r="J34" s="6">
-        <v>7.8399722199999999</v>
+        <v>9.7629999999999999</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="D35">
-        <v>56.951999999999998</v>
+        <v>57.067999999999998</v>
       </c>
       <c r="E35">
-        <v>9.8949999999999996</v>
+        <v>10.125</v>
       </c>
       <c r="F35" s="4">
-        <v>369.87023377922202</v>
+        <v>1633.69</v>
       </c>
       <c r="G35">
-        <v>30033</v>
+        <v>30035</v>
       </c>
       <c r="H35">
-        <v>20015</v>
+        <v>20017</v>
       </c>
       <c r="I35" s="6">
-        <v>56.6</v>
+        <v>56.903399999999998</v>
       </c>
       <c r="J35" s="6">
-        <v>11.21</v>
+        <v>10.6408</v>
       </c>
       <c r="K35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>1466</v>
+        <v>1444</v>
       </c>
       <c r="D36">
-        <v>56.253</v>
+        <v>56.951999999999998</v>
       </c>
       <c r="E36">
-        <v>10.151</v>
+        <v>9.8949999999999996</v>
       </c>
       <c r="F36" s="4">
-        <v>455.99984656104903</v>
+        <v>369.87</v>
       </c>
       <c r="G36">
-        <v>30034</v>
+        <v>30033</v>
       </c>
       <c r="H36">
-        <v>20016</v>
+        <v>20015</v>
       </c>
       <c r="I36" s="6">
-        <v>56.666899999999998</v>
+        <v>56.6</v>
       </c>
       <c r="J36" s="6">
-        <v>11.0266</v>
+        <v>11.21</v>
       </c>
       <c r="K36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>3955</v>
+        <v>3957</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>1437</v>
+        <v>1466</v>
       </c>
       <c r="D37">
-        <v>57.067999999999998</v>
+        <v>56.253</v>
       </c>
       <c r="E37">
-        <v>10.125</v>
+        <v>10.151</v>
       </c>
       <c r="F37" s="4">
-        <v>1633.68789888624</v>
+        <v>456</v>
       </c>
       <c r="G37">
-        <v>30035</v>
+        <v>30034</v>
       </c>
       <c r="H37">
-        <v>20017</v>
+        <v>20016</v>
       </c>
       <c r="I37" s="6">
-        <v>56.903399</v>
+        <v>56.666899999999998</v>
       </c>
       <c r="J37" s="6">
-        <v>10.64080555</v>
+        <v>11.0266</v>
       </c>
       <c r="K37" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3958</v>
       </c>
@@ -2026,7 +2180,7 @@
         <v>8.5729192889999997</v>
       </c>
       <c r="F38" s="4">
-        <v>265.02512814101698</v>
+        <v>265.02999999999997</v>
       </c>
       <c r="G38">
         <v>30036</v>
@@ -2038,144 +2192,153 @@
         <v>55.6</v>
       </c>
       <c r="J38" s="6">
-        <v>7.5819722299999999</v>
+        <v>7.5819999999999999</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3954</v>
+        <v>3959</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>1434</v>
+        <v>1494</v>
       </c>
       <c r="D39">
-        <v>57.098133580000002</v>
+        <v>55.524000000000001</v>
       </c>
       <c r="E39">
-        <v>10.03014217</v>
+        <v>8.7149999999999999</v>
       </c>
       <c r="F39" s="4">
-        <v>233.308208569953</v>
+        <v>64.569999999999993</v>
       </c>
       <c r="G39">
-        <v>30037</v>
+        <v>30032</v>
       </c>
       <c r="H39">
-        <v>20019</v>
+        <v>20014</v>
       </c>
       <c r="I39" s="6">
-        <v>57.55</v>
+        <v>55.485999999999997</v>
       </c>
       <c r="J39" s="6">
-        <v>9.7629999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="K39" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40">
+        <v>3960</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>1461</v>
+      </c>
+      <c r="D40">
+        <v>55.886317130000002</v>
+      </c>
+      <c r="E40">
+        <v>12.15702065</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1935.16</v>
+      </c>
+      <c r="G40">
+        <v>30039</v>
+      </c>
+      <c r="H40">
+        <v>20021</v>
+      </c>
+      <c r="I40" s="6">
+        <v>56.33</v>
+      </c>
+      <c r="J40" s="6">
+        <v>7.64</v>
+      </c>
+      <c r="K40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>3961</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>1461</v>
+      </c>
+      <c r="D41">
+        <v>55.697727649999997</v>
+      </c>
+      <c r="E41">
+        <v>12.58475011</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1632.38</v>
+      </c>
+      <c r="G41">
+        <v>30040</v>
+      </c>
+      <c r="H41">
+        <v>20022</v>
+      </c>
+      <c r="I41" s="6">
+        <v>56.16</v>
+      </c>
+      <c r="J41" s="6">
+        <v>7</v>
+      </c>
+      <c r="K41" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>3962</v>
       </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40">
-        <v>1549</v>
-      </c>
-      <c r="D40">
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>1461</v>
+      </c>
+      <c r="D42">
         <v>55.689498299999997</v>
       </c>
-      <c r="E40">
+      <c r="E42">
         <v>12.06693113</v>
       </c>
-      <c r="F40" s="4">
-        <v>1202.80635079384</v>
-      </c>
-      <c r="G40">
+      <c r="F42" s="4">
+        <v>1202.81</v>
+      </c>
+      <c r="G42">
         <v>30038</v>
       </c>
-      <c r="H40">
+      <c r="H42">
         <v>20020</v>
-      </c>
-      <c r="I40" s="6">
-        <v>56.16</v>
-      </c>
-      <c r="J40" s="6">
-        <v>7</v>
-      </c>
-      <c r="K40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>3960</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41">
-        <v>1523</v>
-      </c>
-      <c r="D41">
-        <v>55.886317130000002</v>
-      </c>
-      <c r="E41">
-        <v>12.15702065</v>
-      </c>
-      <c r="F41" s="4">
-        <v>1935.15539494062</v>
-      </c>
-      <c r="G41">
-        <v>30039</v>
-      </c>
-      <c r="H41">
-        <v>20021</v>
-      </c>
-      <c r="I41" s="6">
-        <v>56.329972230000003</v>
-      </c>
-      <c r="J41" s="6">
-        <v>7.6399722199999998</v>
-      </c>
-      <c r="K41" t="s">
-        <v>30</v>
-      </c>
-      <c r="L41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>3961</v>
-      </c>
-      <c r="B42" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42">
-        <v>1547</v>
-      </c>
-      <c r="D42">
-        <v>55.697727649999997</v>
-      </c>
-      <c r="E42">
-        <v>12.58475011</v>
-      </c>
-      <c r="F42" s="4">
-        <v>1632.38004750593</v>
-      </c>
-      <c r="G42">
-        <v>30040</v>
-      </c>
-      <c r="H42">
-        <v>20022</v>
       </c>
       <c r="I42" s="6">
         <v>56.16</v>
@@ -2189,332 +2352,365 @@
       <c r="L42" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3965</v>
+        <v>3963</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D43">
-        <v>55.653276030000001</v>
+        <v>55.667149510000002</v>
       </c>
       <c r="E43">
-        <v>12.61600567</v>
+        <v>11.419907670000001</v>
       </c>
       <c r="F43" s="4">
-        <v>260.65658207275902</v>
+        <v>248.7</v>
       </c>
       <c r="G43">
-        <v>30041</v>
+        <v>30043</v>
       </c>
       <c r="H43">
-        <v>20023</v>
+        <v>20025</v>
       </c>
       <c r="I43" s="6">
-        <v>55.679972229999997</v>
+        <v>55.59</v>
       </c>
       <c r="J43" s="6">
-        <v>12.82</v>
+        <v>11.01</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>3966</v>
+        <v>3964</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
       </c>
       <c r="C44">
-        <v>1609</v>
+        <v>1558</v>
       </c>
       <c r="D44">
-        <v>54.816173749999997</v>
+        <v>55.658937889999997</v>
       </c>
       <c r="E44">
-        <v>11.43675947</v>
+        <v>12.48010294</v>
       </c>
       <c r="F44" s="4">
-        <v>305.79822477809699</v>
+        <v>2886.15</v>
       </c>
       <c r="G44">
-        <v>30042</v>
+        <v>30045</v>
       </c>
       <c r="H44">
-        <v>20024</v>
+        <v>20027</v>
       </c>
       <c r="I44" s="6">
-        <v>54.55836111</v>
+        <v>55.03</v>
       </c>
       <c r="J44" s="6">
-        <v>11.53066667</v>
+        <v>12.94</v>
       </c>
       <c r="K44" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>3963</v>
+        <v>3965</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
       </c>
       <c r="C45">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="D45">
-        <v>55.667149510000002</v>
+        <v>55.653276030000001</v>
       </c>
       <c r="E45">
-        <v>11.419907670000001</v>
+        <v>12.61600567</v>
       </c>
       <c r="F45" s="4">
-        <v>248.70418172431499</v>
+        <v>260.66000000000003</v>
       </c>
       <c r="G45">
-        <v>30043</v>
+        <v>30041</v>
       </c>
       <c r="H45">
-        <v>20025</v>
+        <v>20023</v>
       </c>
       <c r="I45" s="6">
-        <v>55.59</v>
+        <v>55.68</v>
       </c>
       <c r="J45" s="6">
-        <v>11.00997222</v>
+        <v>12.82</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
       <c r="C46">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D46">
+        <v>54.816173749999997</v>
+      </c>
+      <c r="E46">
+        <v>11.43675947</v>
+      </c>
+      <c r="F46" s="4">
+        <v>305.8</v>
+      </c>
+      <c r="G46">
+        <v>30042</v>
+      </c>
+      <c r="H46">
+        <v>20024</v>
+      </c>
+      <c r="I46" s="6">
+        <v>54.558399999999999</v>
+      </c>
+      <c r="J46" s="6">
+        <v>11.5307</v>
+      </c>
+      <c r="K46" t="s">
+        <v>33</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>3967</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>1461</v>
+      </c>
+      <c r="D47">
         <v>54.790999999999997</v>
       </c>
-      <c r="E46">
+      <c r="E47">
         <v>11.654999999999999</v>
       </c>
-      <c r="F46" s="4">
-        <v>320.71079964960501</v>
-      </c>
-      <c r="G46">
+      <c r="F47" s="4">
+        <v>320.70999999999998</v>
+      </c>
+      <c r="G47">
         <v>30044</v>
       </c>
-      <c r="H46">
+      <c r="H47">
         <v>20026</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I47" s="6">
         <v>56</v>
       </c>
-      <c r="J46" s="6">
+      <c r="J47" s="6">
         <v>7</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K47" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>3964</v>
-      </c>
-      <c r="B47" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47">
-        <v>1558</v>
-      </c>
-      <c r="D47">
-        <v>55.658937889999997</v>
-      </c>
-      <c r="E47">
-        <v>12.48010294</v>
-      </c>
-      <c r="F47" s="4">
-        <v>2886.15281362932</v>
-      </c>
-      <c r="G47">
-        <v>30045</v>
-      </c>
-      <c r="H47">
-        <v>20027</v>
-      </c>
-      <c r="I47" s="6">
-        <v>55.03</v>
-      </c>
-      <c r="J47" s="6">
-        <v>12.93997222</v>
-      </c>
-      <c r="K47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L47" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>3977</v>
+        <v>3974</v>
       </c>
       <c r="B48" t="s">
         <v>7</v>
       </c>
       <c r="C48">
-        <v>3881</v>
+        <v>2652</v>
       </c>
       <c r="D48">
-        <v>43.294310000000003</v>
+        <v>49.094459999999998</v>
       </c>
       <c r="E48">
-        <v>5.4527150000000004</v>
+        <v>6.963946</v>
       </c>
       <c r="F48" s="4">
-        <v>20.792296686701398</v>
+        <v>795.98</v>
       </c>
       <c r="G48">
-        <v>30046</v>
+        <v>30049</v>
       </c>
       <c r="H48">
-        <v>20028</v>
+        <v>20031</v>
       </c>
       <c r="I48" s="6">
-        <v>43.08</v>
+        <v>49.469000000000001</v>
       </c>
       <c r="J48" s="6">
-        <v>4.6059999999999999</v>
+        <v>-0.55200000000000005</v>
       </c>
       <c r="K48" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="B49" t="s">
         <v>7</v>
       </c>
       <c r="C49">
-        <v>3371</v>
+        <v>3148</v>
       </c>
       <c r="D49">
-        <v>45.725746000000001</v>
+        <v>47.143653999999998</v>
       </c>
       <c r="E49">
-        <v>3.2292375999999998</v>
+        <v>3.0309979999999999</v>
       </c>
       <c r="F49" s="4">
-        <v>312.36799208393302</v>
+        <v>757.96</v>
       </c>
       <c r="G49">
-        <v>30047</v>
+        <v>30048</v>
       </c>
       <c r="H49">
-        <v>20029</v>
+        <v>20030</v>
       </c>
       <c r="I49" s="6">
-        <v>46.869972230000002</v>
+        <v>50.15</v>
       </c>
       <c r="J49" s="6">
-        <v>-2.5099722199999999</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="K49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L49" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>3975</v>
+        <v>3976</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
       </c>
       <c r="C50">
-        <v>3148</v>
+        <v>3371</v>
       </c>
       <c r="D50">
-        <v>47.143653999999998</v>
+        <v>45.725746000000001</v>
       </c>
       <c r="E50">
-        <v>3.0309979999999999</v>
+        <v>3.2292375999999998</v>
       </c>
       <c r="F50" s="4">
-        <v>757.95560144553394</v>
+        <v>312.37</v>
       </c>
       <c r="G50">
-        <v>30048</v>
+        <v>30047</v>
       </c>
       <c r="H50">
-        <v>20030</v>
+        <v>20029</v>
       </c>
       <c r="I50" s="6">
-        <v>50.149972220000002</v>
+        <v>46.87</v>
       </c>
       <c r="J50" s="6">
-        <v>1.1200000000000001</v>
+        <v>-2.5099999999999998</v>
       </c>
       <c r="K50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L50" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>3974</v>
+        <v>3977</v>
       </c>
       <c r="B51" t="s">
         <v>7</v>
       </c>
       <c r="C51">
-        <v>2652</v>
+        <v>3881</v>
       </c>
       <c r="D51">
-        <v>49.094459999999998</v>
+        <v>43.294310000000003</v>
       </c>
       <c r="E51">
-        <v>6.963946</v>
+        <v>5.4527150000000004</v>
       </c>
       <c r="F51" s="4">
-        <v>795.97606352372497</v>
+        <v>20.79</v>
       </c>
       <c r="G51">
-        <v>30049</v>
+        <v>30046</v>
       </c>
       <c r="H51">
-        <v>20031</v>
+        <v>20028</v>
       </c>
       <c r="I51" s="6">
-        <v>49.469000000000001</v>
+        <v>43.08</v>
       </c>
       <c r="J51" s="6">
-        <v>-0.55200000000000005</v>
+        <v>4.6059999999999999</v>
       </c>
       <c r="K51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L51" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>3978</v>
       </c>
@@ -2531,7 +2727,7 @@
         <v>5.8780245999999998</v>
       </c>
       <c r="F52" s="4">
-        <v>1310.82467776248</v>
+        <v>1310.82</v>
       </c>
       <c r="G52">
         <v>30050</v>
@@ -2540,10 +2736,10 @@
         <v>20032</v>
       </c>
       <c r="I52" s="6">
-        <v>49.768277779999998</v>
+        <v>49.768300000000004</v>
       </c>
       <c r="J52" s="6">
-        <v>0.38355555000000002</v>
+        <v>0.3836</v>
       </c>
       <c r="K52" t="s">
         <v>22</v>
@@ -2551,691 +2747,751 @@
       <c r="L52" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>4002</v>
+        <v>3989</v>
       </c>
       <c r="B53" t="s">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>4880</v>
+        <v>4843</v>
       </c>
       <c r="D53">
-        <v>51.970735650000002</v>
+        <v>53.454000000000001</v>
       </c>
       <c r="E53">
-        <v>4.302139758</v>
+        <v>6.7640000000000002</v>
       </c>
       <c r="F53" s="4">
-        <v>2034.52527743526</v>
+        <v>996.48</v>
       </c>
       <c r="G53">
-        <v>30051</v>
+        <v>30060</v>
       </c>
       <c r="H53">
-        <v>20033</v>
+        <v>20042</v>
       </c>
       <c r="I53" s="6">
-        <v>52.329972222222203</v>
+        <v>54.247199999999999</v>
       </c>
       <c r="J53" s="6">
-        <v>4.0720000000000001</v>
+        <v>4.1128</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>4006</v>
+        <v>3990</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>4887</v>
+        <v>4809</v>
       </c>
       <c r="D54">
-        <v>51.876159389999998</v>
+        <v>53.435000000000002</v>
       </c>
       <c r="E54">
-        <v>4.368893484</v>
+        <v>6.8609999999999998</v>
       </c>
       <c r="F54" s="4">
-        <v>302.88586073259103</v>
+        <v>265.02999999999997</v>
       </c>
       <c r="G54">
-        <v>30052</v>
+        <v>30056</v>
       </c>
       <c r="H54">
-        <v>20034</v>
+        <v>20038</v>
       </c>
       <c r="I54" s="6">
-        <v>51.75</v>
+        <v>54.276000000000003</v>
       </c>
       <c r="J54" s="6">
-        <v>3.06</v>
+        <v>5.58</v>
       </c>
       <c r="K54" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>3995</v>
+        <v>3991</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>4821</v>
+        <v>4810</v>
       </c>
       <c r="D55">
-        <v>53.374663069999997</v>
+        <v>53.433578220000001</v>
       </c>
       <c r="E55">
-        <v>6.8055336439999996</v>
+        <v>6.8181479070000002</v>
       </c>
       <c r="F55" s="4">
-        <v>610.35758323057905</v>
+        <v>211.99</v>
       </c>
       <c r="G55">
-        <v>30053</v>
+        <v>30055</v>
       </c>
       <c r="H55">
-        <v>20035</v>
+        <v>20037</v>
       </c>
       <c r="I55" s="6">
-        <v>54.271999999999998</v>
+        <v>52.6</v>
       </c>
       <c r="J55" s="6">
-        <v>5.577</v>
+        <v>4.42</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>4815</v>
+        <v>4812</v>
       </c>
       <c r="D56">
-        <v>53.398854630000002</v>
+        <v>53.421701089999999</v>
       </c>
       <c r="E56">
-        <v>6.7755266619999999</v>
+        <v>6.8898715609999996</v>
       </c>
       <c r="F56" s="4">
-        <v>286.86785848231</v>
+        <v>77.37</v>
       </c>
       <c r="G56">
-        <v>30054</v>
+        <v>30063</v>
       </c>
       <c r="H56">
-        <v>20036</v>
+        <v>20045</v>
       </c>
       <c r="I56" s="6">
-        <v>54.036000000000001</v>
+        <v>52.72</v>
       </c>
       <c r="J56" s="6">
-        <v>5.9630000000000001</v>
+        <v>5.58</v>
       </c>
       <c r="K56" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>3991</v>
+        <v>3993</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>4810</v>
+        <v>4815</v>
       </c>
       <c r="D57">
-        <v>53.433578220000001</v>
+        <v>53.398854630000002</v>
       </c>
       <c r="E57">
-        <v>6.8181479070000002</v>
+        <v>6.7755266619999999</v>
       </c>
       <c r="F57" s="4">
-        <v>211.990707279297</v>
+        <v>286.87</v>
       </c>
       <c r="G57">
-        <v>30055</v>
+        <v>30054</v>
       </c>
       <c r="H57">
-        <v>20037</v>
+        <v>20036</v>
       </c>
       <c r="I57" s="6">
-        <v>52.6</v>
+        <v>54.036000000000001</v>
       </c>
       <c r="J57" s="6">
-        <v>4.42</v>
+        <v>5.9630000000000001</v>
       </c>
       <c r="K57" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L57" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>3990</v>
+        <v>3994</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>4809</v>
+        <v>4816</v>
       </c>
       <c r="D58">
-        <v>53.435000000000002</v>
+        <v>53.394521580000003</v>
       </c>
       <c r="E58">
-        <v>6.8609999999999998</v>
+        <v>6.8932625610000002</v>
       </c>
       <c r="F58" s="4">
-        <v>265.02512814101698</v>
+        <v>320.10000000000002</v>
       </c>
       <c r="G58">
-        <v>30056</v>
+        <v>30066</v>
       </c>
       <c r="H58">
-        <v>20038</v>
+        <v>20048</v>
       </c>
       <c r="I58" s="6">
-        <v>54.276000000000003</v>
+        <v>53</v>
       </c>
       <c r="J58" s="6">
-        <v>5.58</v>
+        <v>5.26</v>
       </c>
       <c r="K58" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>4004</v>
+        <v>3995</v>
       </c>
       <c r="B59" t="s">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>4884</v>
+        <v>4821</v>
       </c>
       <c r="D59">
-        <v>51.931135660000002</v>
+        <v>53.374663069999997</v>
       </c>
       <c r="E59">
-        <v>4.3779014719999996</v>
+        <v>6.8055336439999996</v>
       </c>
       <c r="F59" s="4">
-        <v>2152.4214741584201</v>
+        <v>610.36</v>
       </c>
       <c r="G59">
-        <v>30057</v>
+        <v>30053</v>
       </c>
       <c r="H59">
-        <v>20039</v>
+        <v>20035</v>
       </c>
       <c r="I59" s="6">
-        <v>52.914000000000001</v>
+        <v>54.271999999999998</v>
       </c>
       <c r="J59" s="6">
-        <v>3.5779999999999998</v>
+        <v>5.577</v>
       </c>
       <c r="K59" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="B60" t="s">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>4828</v>
+        <v>4873</v>
       </c>
       <c r="D60">
-        <v>53.319677159999998</v>
+        <v>53.370972790000003</v>
       </c>
       <c r="E60">
-        <v>6.7061180409999999</v>
+        <v>6.8516161819999999</v>
       </c>
       <c r="F60" s="4">
-        <v>413.68680641183698</v>
+        <v>451.42</v>
       </c>
       <c r="G60">
-        <v>30058</v>
+        <v>30067</v>
       </c>
       <c r="H60">
-        <v>20040</v>
+        <v>20049</v>
       </c>
       <c r="I60" s="6">
-        <v>53.000176000000003</v>
+        <v>53.1721</v>
       </c>
       <c r="J60" s="6">
-        <v>3.5779999999999998</v>
+        <v>4.0952000000000002</v>
       </c>
       <c r="K60" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L60" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>4003</v>
+        <v>3997</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>4883</v>
+        <v>4823</v>
       </c>
       <c r="D61">
-        <v>51.941737570000001</v>
+        <v>53.362059510000002</v>
       </c>
       <c r="E61">
-        <v>4.2463334760000002</v>
+        <v>6.9448501089999999</v>
       </c>
       <c r="F61" s="4">
-        <v>245.15126484254</v>
+        <v>280.68</v>
       </c>
       <c r="G61">
-        <v>30059</v>
+        <v>30062</v>
       </c>
       <c r="H61">
-        <v>20041</v>
+        <v>20044</v>
       </c>
       <c r="I61" s="6">
-        <v>52.98</v>
+        <v>52.594299999999997</v>
       </c>
       <c r="J61" s="6">
-        <v>3.5779999999999998</v>
+        <v>4.2125000000000004</v>
       </c>
       <c r="K61" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>3989</v>
+        <v>3998</v>
       </c>
       <c r="B62" t="s">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>4808</v>
+        <v>4828</v>
       </c>
       <c r="D62">
-        <v>53.454000000000001</v>
+        <v>53.319677159999998</v>
       </c>
       <c r="E62">
-        <v>6.7640000000000002</v>
+        <v>6.7061180409999999</v>
       </c>
       <c r="F62" s="4">
-        <v>996.48</v>
+        <v>413.69</v>
       </c>
       <c r="G62">
-        <v>30060</v>
+        <v>30058</v>
       </c>
       <c r="H62">
-        <v>20042</v>
+        <v>20040</v>
       </c>
       <c r="I62" s="6">
-        <v>54.247199999999999</v>
+        <v>53.0002</v>
       </c>
       <c r="J62" s="6">
-        <v>4.1128</v>
+        <v>3.5779999999999998</v>
       </c>
       <c r="K62" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>4005</v>
+        <v>3999</v>
       </c>
       <c r="B63" t="s">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>4885</v>
+        <v>4829</v>
       </c>
       <c r="D63">
-        <v>51.911361339999999</v>
+        <v>53.317028809999996</v>
       </c>
       <c r="E63">
-        <v>4.2375048800000004</v>
+        <v>6.7598854460000002</v>
       </c>
       <c r="F63" s="4">
-        <v>860.96858966337095</v>
+        <v>246.34</v>
       </c>
       <c r="G63">
-        <v>30061</v>
+        <v>30064</v>
       </c>
       <c r="H63">
-        <v>20043</v>
+        <v>20046</v>
       </c>
       <c r="I63" s="6">
-        <v>53.036999999999999</v>
+        <v>54.036000000000001</v>
       </c>
       <c r="J63" s="6">
-        <v>3.1920000000000002</v>
+        <v>5.9</v>
       </c>
       <c r="K63" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L63" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>3997</v>
+        <v>4000</v>
       </c>
       <c r="B64" t="s">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>4823</v>
+        <v>4870</v>
       </c>
       <c r="D64">
-        <v>53.362059510000002</v>
+        <v>52.20669187</v>
       </c>
       <c r="E64">
-        <v>6.9448501089999999</v>
+        <v>4.8731760629999998</v>
       </c>
       <c r="F64" s="4">
-        <v>280.680433660299</v>
+        <v>542.54</v>
       </c>
       <c r="G64">
-        <v>30062</v>
+        <v>30069</v>
       </c>
       <c r="H64">
-        <v>20044</v>
+        <v>20051</v>
       </c>
       <c r="I64" s="6">
-        <v>52.594333333333303</v>
+        <v>52.67</v>
       </c>
       <c r="J64" s="6">
-        <v>4.2125277777777699</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="K64" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L64" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>3992</v>
+        <v>4001</v>
       </c>
       <c r="B65" t="s">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>4812</v>
+        <v>4874</v>
       </c>
       <c r="D65">
-        <v>53.421701089999999</v>
+        <v>52.065654430000002</v>
       </c>
       <c r="E65">
-        <v>6.8898715609999996</v>
+        <v>4.8516698500000004</v>
       </c>
       <c r="F65" s="4">
-        <v>77.366685345865903</v>
+        <v>557.17999999999995</v>
       </c>
       <c r="G65">
-        <v>30063</v>
+        <v>30065</v>
       </c>
       <c r="H65">
-        <v>20045</v>
+        <v>20047</v>
       </c>
       <c r="I65" s="6">
-        <v>52.719972222222196</v>
+        <v>52.68</v>
       </c>
       <c r="J65" s="6">
-        <v>5.58</v>
+        <v>3.77</v>
       </c>
       <c r="K65" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>3999</v>
+        <v>4002</v>
       </c>
       <c r="B66" t="s">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>4829</v>
+        <v>4880</v>
       </c>
       <c r="D66">
-        <v>53.317028809999996</v>
+        <v>51.970735650000002</v>
       </c>
       <c r="E66">
-        <v>6.7598854460000002</v>
+        <v>4.302139758</v>
       </c>
       <c r="F66" s="4">
-        <v>246.335570469798</v>
+        <v>2034.53</v>
       </c>
       <c r="G66">
-        <v>30064</v>
+        <v>30051</v>
       </c>
       <c r="H66">
-        <v>20046</v>
+        <v>20033</v>
       </c>
       <c r="I66" s="6">
-        <v>54.036000000000001</v>
+        <v>52.33</v>
       </c>
       <c r="J66" s="6">
-        <v>5.9</v>
+        <v>4.0720000000000001</v>
       </c>
       <c r="K66" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>4001</v>
+        <v>4003</v>
       </c>
       <c r="B67" t="s">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>4874</v>
+        <v>4883</v>
       </c>
       <c r="D67">
-        <v>52.065654430000002</v>
+        <v>51.941737570000001</v>
       </c>
       <c r="E67">
-        <v>4.8516698500000004</v>
+        <v>4.2463334760000002</v>
       </c>
       <c r="F67" s="4">
-        <v>557.18324446660699</v>
+        <v>245.15</v>
       </c>
       <c r="G67">
-        <v>30065</v>
+        <v>30059</v>
       </c>
       <c r="H67">
-        <v>20047</v>
+        <v>20041</v>
       </c>
       <c r="I67" s="6">
-        <v>52.68</v>
+        <v>52.98</v>
       </c>
       <c r="J67" s="6">
-        <v>3.77</v>
+        <v>3.5779999999999998</v>
       </c>
       <c r="K67" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>3994</v>
+        <v>4004</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>4816</v>
+        <v>4884</v>
       </c>
       <c r="D68">
-        <v>53.394521580000003</v>
+        <v>51.931135660000002</v>
       </c>
       <c r="E68">
-        <v>6.8932625610000002</v>
+        <v>4.3779014719999996</v>
       </c>
       <c r="F68" s="4">
-        <v>320.10466061851997</v>
+        <v>2152.42</v>
       </c>
       <c r="G68">
-        <v>30066</v>
+        <v>30057</v>
       </c>
       <c r="H68">
-        <v>20048</v>
+        <v>20039</v>
       </c>
       <c r="I68" s="6">
-        <v>53</v>
+        <v>52.914000000000001</v>
       </c>
       <c r="J68" s="6">
-        <v>5.2599722222222196</v>
+        <v>3.5779999999999998</v>
       </c>
       <c r="K68" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L68" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>3996</v>
+        <v>4005</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>4822</v>
+        <v>4885</v>
       </c>
       <c r="D69">
-        <v>53.370972790000003</v>
+        <v>51.911361339999999</v>
       </c>
       <c r="E69">
-        <v>6.8516161819999999</v>
+        <v>4.2375048800000004</v>
       </c>
       <c r="F69" s="4">
-        <v>451.41642705338103</v>
+        <v>860.97</v>
       </c>
       <c r="G69">
-        <v>30067</v>
+        <v>30061</v>
       </c>
       <c r="H69">
-        <v>20049</v>
+        <v>20043</v>
       </c>
       <c r="I69" s="6">
-        <v>53.1721</v>
+        <v>53.036999999999999</v>
       </c>
       <c r="J69" s="6">
-        <v>4.0952000000000002</v>
+        <v>3.1920000000000002</v>
       </c>
       <c r="K69" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L69" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>4890</v>
+        <v>4887</v>
       </c>
       <c r="D70">
-        <v>51.802126800000003</v>
+        <v>51.876159389999998</v>
       </c>
       <c r="E70">
-        <v>4.3527692489999996</v>
+        <v>4.368893484</v>
       </c>
       <c r="F70" s="4">
-        <v>870.6</v>
+        <v>302.89</v>
       </c>
       <c r="G70">
-        <v>30068</v>
+        <v>30052</v>
       </c>
       <c r="H70">
-        <v>20050</v>
+        <v>20034</v>
       </c>
       <c r="I70" s="6">
-        <v>51.739998999999997</v>
+        <v>51.75</v>
       </c>
       <c r="J70" s="6">
-        <v>2.879972</v>
+        <v>3.06</v>
       </c>
       <c r="K70" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>4000</v>
+        <v>4007</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>4870</v>
+        <v>4890</v>
       </c>
       <c r="D71">
-        <v>52.20669187</v>
+        <v>51.802126800000003</v>
       </c>
       <c r="E71">
-        <v>4.8731760629999998</v>
+        <v>4.3527692489999996</v>
       </c>
       <c r="F71" s="4">
-        <v>542.540073982737</v>
+        <v>870.6</v>
       </c>
       <c r="G71">
-        <v>30069</v>
+        <v>30068</v>
       </c>
       <c r="H71">
-        <v>20051</v>
+        <v>20050</v>
       </c>
       <c r="I71" s="6">
-        <v>52.67</v>
+        <v>51.74</v>
       </c>
       <c r="J71" s="6">
-        <v>4.2699722222222203</v>
+        <v>2.88</v>
       </c>
       <c r="K71" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>4008</v>
       </c>
@@ -3252,7 +3508,7 @@
         <v>10.281000000000001</v>
       </c>
       <c r="F72" s="4">
-        <v>339.29041130141201</v>
+        <v>339.29</v>
       </c>
       <c r="G72">
         <v>30070</v>
@@ -3266,877 +3522,1078 @@
       <c r="J72" s="6">
         <v>10.281000000000001</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>4038</v>
+        <v>4027</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73">
-        <v>5661</v>
+        <v>5543</v>
       </c>
       <c r="D73">
-        <v>53.813650869999996</v>
+        <v>57.524999999999999</v>
       </c>
       <c r="E73">
-        <v>-0.33496250399999999</v>
+        <v>-1.744</v>
       </c>
       <c r="F73" s="4">
-        <v>429.57369671208897</v>
+        <v>435.4</v>
       </c>
       <c r="G73">
-        <v>30071</v>
+        <v>30083</v>
       </c>
       <c r="H73">
-        <v>20052</v>
+        <v>5543</v>
       </c>
       <c r="I73" s="6">
-        <v>54.039972222222197</v>
+        <v>57.524999999999999</v>
       </c>
       <c r="J73" s="6">
-        <v>1.27</v>
-      </c>
-      <c r="K73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+        <v>-1.744</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>4035</v>
+        <v>4028</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
       <c r="C74">
-        <v>5650</v>
+        <v>5545</v>
       </c>
       <c r="D74">
-        <v>54.506819880000002</v>
+        <v>57.524000000000001</v>
       </c>
       <c r="E74">
-        <v>-2.6847810820000002</v>
+        <v>-2.9910000000000001</v>
       </c>
       <c r="F74" s="4">
-        <v>211.990707279297</v>
+        <v>1288.72</v>
       </c>
       <c r="G74">
-        <v>30072</v>
+        <v>30074</v>
       </c>
       <c r="H74">
-        <v>20053</v>
+        <v>20055</v>
       </c>
       <c r="I74" s="6">
-        <v>54.088000000000001</v>
+        <v>58.188000000000002</v>
       </c>
       <c r="J74" s="6">
-        <v>-3.4369722222222201</v>
+        <v>-2.72</v>
       </c>
       <c r="K74" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>4043</v>
+        <v>4029</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
       <c r="C75">
-        <v>5735</v>
+        <v>5549</v>
       </c>
       <c r="D75">
-        <v>52.939</v>
+        <v>57.483122940000001</v>
       </c>
       <c r="E75">
-        <v>-0.2</v>
+        <v>-2.1708429499999999</v>
       </c>
       <c r="F75" s="4">
-        <v>1424.9030158928699</v>
+        <v>859.15</v>
       </c>
       <c r="G75">
-        <v>30073</v>
+        <v>30081</v>
       </c>
       <c r="H75">
-        <v>20054</v>
+        <v>20062</v>
       </c>
       <c r="I75" s="6">
-        <v>53.57</v>
+        <v>58.41</v>
       </c>
       <c r="J75" s="6">
-        <v>1.29</v>
+        <v>-1.23</v>
       </c>
       <c r="K75" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>4028</v>
+        <v>4030</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76">
-        <v>5545</v>
+        <v>5555</v>
       </c>
       <c r="D76">
-        <v>57.524000000000001</v>
+        <v>57.368732299999998</v>
       </c>
       <c r="E76">
-        <v>-2.9910000000000001</v>
+        <v>-2.4336748890000002</v>
       </c>
       <c r="F76" s="4">
-        <v>1288.72109013626</v>
+        <v>1597.1</v>
       </c>
       <c r="G76">
-        <v>30074</v>
+        <v>30085</v>
       </c>
       <c r="H76">
-        <v>20055</v>
+        <v>20065</v>
       </c>
       <c r="I76" s="6">
-        <v>58.188000000000002</v>
+        <v>58.146000000000001</v>
       </c>
       <c r="J76" s="6">
-        <v>-2.72</v>
+        <v>-0.62</v>
       </c>
       <c r="K76" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>4037</v>
+        <v>4031</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77">
-        <v>5656</v>
+        <v>5594</v>
       </c>
       <c r="D77">
-        <v>53.883398190000001</v>
+        <v>55.945</v>
       </c>
       <c r="E77">
-        <v>-2.7411721600000001</v>
+        <v>-3.2610000000000001</v>
       </c>
       <c r="F77" s="4">
-        <v>1718.29478684835</v>
+        <v>546.72</v>
       </c>
       <c r="G77">
-        <v>30075</v>
+        <v>30087</v>
       </c>
       <c r="H77">
-        <v>20056</v>
+        <v>20067</v>
       </c>
       <c r="I77" s="6">
-        <v>54</v>
+        <v>56.610999999999997</v>
       </c>
       <c r="J77" s="6">
-        <v>-3.99</v>
+        <v>-1.821</v>
       </c>
       <c r="K77" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>4048</v>
+        <v>4032</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
       <c r="C78">
-        <v>5779</v>
+        <v>5596</v>
       </c>
       <c r="D78">
-        <v>52.059813949999999</v>
+        <v>55.906131809999998</v>
       </c>
       <c r="E78">
-        <v>1.1579766359999999</v>
+        <v>-2.6916634259999999</v>
       </c>
       <c r="F78" s="4">
-        <v>3495.5324740332799</v>
+        <v>418.99</v>
       </c>
       <c r="G78">
-        <v>30076</v>
+        <v>30091</v>
       </c>
       <c r="H78">
-        <v>20057</v>
+        <v>20071</v>
       </c>
       <c r="I78" s="6">
-        <v>51.772694444444397</v>
+        <v>56.267000000000003</v>
       </c>
       <c r="J78" s="6">
-        <v>1.98197222222222</v>
+        <v>-2.25</v>
       </c>
       <c r="K78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>4046</v>
+        <v>4033</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79">
-        <v>5750</v>
+        <v>5605</v>
       </c>
       <c r="D79">
-        <v>52.573999999999998</v>
+        <v>55.8176001</v>
       </c>
       <c r="E79">
-        <v>1.2669999999999999</v>
+        <v>-2.7248958220000001</v>
       </c>
       <c r="F79" s="4">
-        <v>1114.3664889332099</v>
+        <v>877.64</v>
       </c>
       <c r="G79">
-        <v>30077</v>
+        <v>30095</v>
       </c>
       <c r="H79">
-        <v>20058</v>
+        <v>20075</v>
       </c>
       <c r="I79" s="6">
-        <v>52.7</v>
+        <v>56.49</v>
       </c>
       <c r="J79" s="6">
-        <v>2.8599722222222201</v>
+        <v>-2.1949999999999998</v>
       </c>
       <c r="K79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>4047</v>
+        <v>4034</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80">
-        <v>5778</v>
+        <v>5637</v>
       </c>
       <c r="D80">
-        <v>52.073</v>
+        <v>55.039000000000001</v>
       </c>
       <c r="E80">
-        <v>1.1000000000000001</v>
+        <v>-1.4710000000000001</v>
       </c>
       <c r="F80" s="4">
-        <v>241.77089170583099</v>
+        <v>1898.89</v>
       </c>
       <c r="G80">
-        <v>30078</v>
+        <v>30089</v>
       </c>
       <c r="H80">
-        <v>20059</v>
+        <v>20069</v>
       </c>
       <c r="I80" s="6">
-        <v>51.625972222222202</v>
+        <v>54.98</v>
       </c>
       <c r="J80" s="6">
-        <v>1.49597222222222</v>
+        <v>1.68</v>
       </c>
       <c r="K80" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>4049</v>
+        <v>4035</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
       <c r="C81">
-        <v>5861</v>
+        <v>5650</v>
       </c>
       <c r="D81">
-        <v>51.307353810000002</v>
+        <v>54.506819880000002</v>
       </c>
       <c r="E81">
-        <v>1.0074736950000001</v>
+        <v>-2.6847810820000002</v>
       </c>
       <c r="F81" s="4">
-        <v>199.99999999999901</v>
+        <v>211.99</v>
       </c>
       <c r="G81">
-        <v>30079</v>
+        <v>30072</v>
       </c>
       <c r="H81">
-        <v>20060</v>
+        <v>20053</v>
       </c>
       <c r="I81" s="6">
-        <v>51.46</v>
+        <v>54.088000000000001</v>
       </c>
       <c r="J81" s="6">
-        <v>1.09297222222222</v>
+        <v>-3.4369999999999998</v>
       </c>
       <c r="K81" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>4039</v>
+        <v>4036</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
       <c r="C82">
-        <v>5666</v>
+        <v>5654</v>
       </c>
       <c r="D82">
-        <v>53.790999999999997</v>
+        <v>54.0138319</v>
       </c>
       <c r="E82">
-        <v>-0.40799999999999997</v>
+        <v>-2.7372891460000002</v>
       </c>
       <c r="F82" s="4">
-        <v>968.58966337129198</v>
+        <v>1156.93</v>
       </c>
       <c r="G82">
-        <v>30080</v>
+        <v>30094</v>
       </c>
       <c r="H82">
-        <v>20061</v>
+        <v>20074</v>
       </c>
       <c r="I82" s="6">
-        <v>53.92</v>
+        <v>53.810400000000001</v>
       </c>
       <c r="J82" s="6">
-        <v>1.56</v>
+        <v>-4.9074</v>
       </c>
       <c r="K82" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>4029</v>
+        <v>4037</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
       <c r="C83">
-        <v>5549</v>
+        <v>5656</v>
       </c>
       <c r="D83">
-        <v>57.483122940000001</v>
+        <v>53.883398190000001</v>
       </c>
       <c r="E83">
-        <v>-2.1708429499999999</v>
+        <v>-2.7411721600000001</v>
       </c>
       <c r="F83" s="4">
-        <v>859.14739342417795</v>
+        <v>1718.29</v>
       </c>
       <c r="G83">
-        <v>30081</v>
+        <v>30075</v>
       </c>
       <c r="H83">
-        <v>20062</v>
+        <v>20056</v>
       </c>
       <c r="I83" s="6">
-        <v>58.409972222222201</v>
+        <v>54</v>
       </c>
       <c r="J83" s="6">
-        <v>-1.22997222222222</v>
+        <v>-3.99</v>
       </c>
       <c r="K83" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>4050</v>
+        <v>4038</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
       <c r="C84">
-        <v>5862</v>
+        <v>5661</v>
       </c>
       <c r="D84">
-        <v>51.301000000000002</v>
+        <v>53.813650869999996</v>
       </c>
       <c r="E84">
-        <v>1.131</v>
+        <v>-0.33496250399999999</v>
       </c>
       <c r="F84" s="4">
-        <v>273.73481913383699</v>
+        <v>429.57</v>
       </c>
       <c r="G84">
-        <v>30082</v>
+        <v>30071</v>
       </c>
       <c r="H84">
-        <v>20063</v>
+        <v>20052</v>
       </c>
       <c r="I84" s="6">
-        <v>51.429972222222197</v>
+        <v>54.04</v>
       </c>
       <c r="J84" s="6">
-        <v>1.633</v>
+        <v>1.27</v>
       </c>
       <c r="K84" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>4027</v>
+        <v>4039</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
       <c r="C85">
-        <v>5543</v>
+        <v>5666</v>
       </c>
       <c r="D85">
-        <v>57.524999999999999</v>
+        <v>53.790999999999997</v>
       </c>
       <c r="E85">
-        <v>-1.744</v>
+        <v>-0.40799999999999997</v>
       </c>
       <c r="F85" s="4">
-        <v>435.3984248031</v>
+        <v>968.59</v>
       </c>
       <c r="G85">
-        <v>30083</v>
+        <v>30080</v>
       </c>
       <c r="H85">
-        <v>5543</v>
+        <v>20061</v>
       </c>
       <c r="I85" s="6">
-        <v>57.524999999999999</v>
+        <v>53.92</v>
       </c>
       <c r="J85" s="6">
-        <v>-1.744</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.56</v>
+      </c>
+      <c r="K85" t="s">
+        <v>67</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>4045</v>
+        <v>4040</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86">
-        <v>5744</v>
+        <v>5684</v>
       </c>
       <c r="D86">
-        <v>52.695177540000003</v>
+        <v>53.650049950000003</v>
       </c>
       <c r="E86">
-        <v>0.75472292399999996</v>
+        <v>-0.63843005799999997</v>
       </c>
       <c r="F86" s="4">
-        <v>609.41999999999996</v>
+        <v>323.32</v>
       </c>
       <c r="G86">
-        <v>30084</v>
+        <v>30086</v>
       </c>
       <c r="H86">
-        <v>20064</v>
+        <v>20066</v>
       </c>
       <c r="I86" s="6">
-        <v>53.478972222222197</v>
+        <v>54.63</v>
       </c>
       <c r="J86" s="6">
-        <v>0.83697222222222201</v>
+        <v>1.48</v>
       </c>
       <c r="K86" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>4030</v>
+        <v>4041</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
       <c r="C87">
-        <v>5555</v>
+        <v>5715</v>
       </c>
       <c r="D87">
-        <v>57.368732299999998</v>
+        <v>53.372731160000001</v>
       </c>
       <c r="E87">
-        <v>-2.4336748890000002</v>
+        <v>-3.02784721</v>
       </c>
       <c r="F87" s="4">
-        <v>1597.09673382555</v>
+        <v>2757.25</v>
       </c>
       <c r="G87">
-        <v>30085</v>
+        <v>30093</v>
       </c>
       <c r="H87">
-        <v>20065</v>
+        <v>20073</v>
       </c>
       <c r="I87" s="6">
-        <v>58.146000000000001</v>
+        <v>53.72</v>
       </c>
       <c r="J87" s="6">
-        <v>-0.62</v>
+        <v>-3.92</v>
       </c>
       <c r="K87" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>4040</v>
+        <v>4042</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88">
-        <v>5684</v>
+        <v>5730</v>
       </c>
       <c r="D88">
-        <v>53.650049950000003</v>
+        <v>53.208529660000004</v>
       </c>
       <c r="E88">
-        <v>-0.63843005799999997</v>
+        <v>-3.6062240060000001</v>
       </c>
       <c r="F88" s="4">
-        <v>323.31543624160997</v>
+        <v>319.74</v>
       </c>
       <c r="G88">
-        <v>30086</v>
+        <v>30092</v>
       </c>
       <c r="H88">
-        <v>20066</v>
+        <v>20072</v>
       </c>
       <c r="I88" s="6">
-        <v>54.63</v>
+        <v>53.46</v>
       </c>
       <c r="J88" s="6">
-        <v>1.47997222222222</v>
+        <v>-3.5990000000000002</v>
       </c>
       <c r="K88" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>4031</v>
+        <v>4043</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
       <c r="C89">
-        <v>5594</v>
+        <v>5735</v>
       </c>
       <c r="D89">
-        <v>55.945</v>
+        <v>52.939</v>
       </c>
       <c r="E89">
-        <v>-3.2610000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="F89" s="4">
-        <v>546.71505443624005</v>
+        <v>1424.9</v>
       </c>
       <c r="G89">
-        <v>30087</v>
+        <v>30073</v>
       </c>
       <c r="H89">
-        <v>20067</v>
+        <v>20054</v>
       </c>
       <c r="I89" s="6">
-        <v>56.610972222222202</v>
+        <v>53.57</v>
       </c>
       <c r="J89" s="6">
-        <v>-1.82097222222222</v>
+        <v>1.29</v>
       </c>
       <c r="K89" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>4051</v>
+        <v>4044</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
       <c r="C90">
-        <v>5875</v>
+        <v>5741</v>
       </c>
       <c r="D90">
-        <v>50.941162040000002</v>
+        <v>52.814999999999998</v>
       </c>
       <c r="E90">
-        <v>-0.52488235000000005</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="F90" s="4">
-        <v>1939.8926174496601</v>
+        <v>345.12</v>
       </c>
       <c r="G90">
-        <v>30088</v>
+        <v>30090</v>
       </c>
       <c r="H90">
-        <v>20068</v>
+        <v>20070</v>
       </c>
       <c r="I90" s="6">
-        <v>50.659972222222201</v>
+        <v>53.134999999999998</v>
       </c>
       <c r="J90" s="6">
-        <v>-0.2</v>
+        <v>1.147</v>
       </c>
       <c r="K90" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>4034</v>
+        <v>4045</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
       <c r="C91">
-        <v>5637</v>
+        <v>5744</v>
       </c>
       <c r="D91">
-        <v>55.039000000000001</v>
+        <v>52.695177540000003</v>
       </c>
       <c r="E91">
-        <v>-1.4710000000000001</v>
+        <v>0.75472292399999996</v>
       </c>
       <c r="F91" s="4">
-        <v>1898.89025893958</v>
+        <v>609.41999999999996</v>
       </c>
       <c r="G91">
-        <v>30089</v>
+        <v>30084</v>
       </c>
       <c r="H91">
-        <v>20069</v>
+        <v>20064</v>
       </c>
       <c r="I91" s="6">
-        <v>54.979972222222202</v>
+        <v>53.478999999999999</v>
       </c>
       <c r="J91" s="6">
-        <v>1.67997222222222</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="K91" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>4044</v>
+        <v>4046</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
       <c r="C92">
-        <v>5741</v>
+        <v>5750</v>
       </c>
       <c r="D92">
-        <v>52.814999999999998</v>
+        <v>52.573999999999998</v>
       </c>
       <c r="E92">
-        <v>0.23899999999999999</v>
+        <v>1.2669999999999999</v>
       </c>
       <c r="F92" s="4">
-        <v>345.115139392424</v>
+        <v>1114.3699999999999</v>
       </c>
       <c r="G92">
-        <v>30090</v>
+        <v>30077</v>
       </c>
       <c r="H92">
-        <v>20070</v>
+        <v>20058</v>
       </c>
       <c r="I92" s="6">
-        <v>53.134972222222203</v>
+        <v>52.7</v>
       </c>
       <c r="J92" s="6">
-        <v>1.147</v>
+        <v>2.86</v>
       </c>
       <c r="K92" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>4032</v>
+        <v>4047</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
       <c r="C93">
-        <v>5596</v>
+        <v>5778</v>
       </c>
       <c r="D93">
-        <v>55.906131809999998</v>
+        <v>52.073</v>
       </c>
       <c r="E93">
-        <v>-2.6916634259999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F93" s="4">
-        <v>418.98895532620497</v>
+        <v>241.77</v>
       </c>
       <c r="G93">
-        <v>30091</v>
+        <v>30078</v>
       </c>
       <c r="H93">
-        <v>20071</v>
+        <v>20059</v>
       </c>
       <c r="I93" s="6">
-        <v>56.267000000000003</v>
+        <v>51.625999999999998</v>
       </c>
       <c r="J93" s="6">
-        <v>-2.25</v>
+        <v>1.496</v>
       </c>
       <c r="K93" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>4042</v>
+        <v>4048</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94">
-        <v>5730</v>
+        <v>5779</v>
       </c>
       <c r="D94">
-        <v>53.208529660000004</v>
+        <v>52.059813949999999</v>
       </c>
       <c r="E94">
-        <v>-3.6062240060000001</v>
+        <v>1.1579766359999999</v>
       </c>
       <c r="F94" s="4">
-        <v>319.73953738156399</v>
+        <v>3495.53</v>
       </c>
       <c r="G94">
-        <v>30092</v>
+        <v>30076</v>
       </c>
       <c r="H94">
-        <v>20072</v>
+        <v>20057</v>
       </c>
       <c r="I94" s="6">
-        <v>53.46</v>
+        <v>51.7727</v>
       </c>
       <c r="J94" s="6">
-        <v>-3.5990000000000002</v>
+        <v>1.982</v>
       </c>
       <c r="K94" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>4041</v>
+        <v>4049</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
       <c r="C95">
-        <v>5715</v>
+        <v>5861</v>
       </c>
       <c r="D95">
-        <v>53.372731160000001</v>
+        <v>51.307353810000002</v>
       </c>
       <c r="E95">
-        <v>-3.02784721</v>
+        <v>1.0074736950000001</v>
       </c>
       <c r="F95" s="4">
-        <v>2757.2519083969401</v>
+        <v>200</v>
       </c>
       <c r="G95">
-        <v>30093</v>
+        <v>30079</v>
       </c>
       <c r="H95">
-        <v>20073</v>
+        <v>20060</v>
       </c>
       <c r="I95" s="6">
-        <v>53.719972222222196</v>
+        <v>51.46</v>
       </c>
       <c r="J95" s="6">
-        <v>-3.9199722222222202</v>
+        <v>1.093</v>
       </c>
       <c r="K95" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>4036</v>
+        <v>4050</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
       <c r="C96">
-        <v>5654</v>
+        <v>5862</v>
       </c>
       <c r="D96">
-        <v>54.0138319</v>
+        <v>51.301000000000002</v>
       </c>
       <c r="E96">
-        <v>-2.7372891460000002</v>
+        <v>1.131</v>
       </c>
       <c r="F96" s="4">
-        <v>1156.9265423601501</v>
+        <v>273.73</v>
       </c>
       <c r="G96">
-        <v>30094</v>
+        <v>30082</v>
       </c>
       <c r="H96">
-        <v>20074</v>
+        <v>20063</v>
       </c>
       <c r="I96" s="6">
-        <v>53.810416666666598</v>
+        <v>51.43</v>
       </c>
       <c r="J96" s="6">
-        <v>-4.9074166666666601</v>
+        <v>1.633</v>
       </c>
       <c r="K96" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>4033</v>
+        <v>4051</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97">
-        <v>5605</v>
+        <v>5875</v>
       </c>
       <c r="D97">
-        <v>55.8176001</v>
+        <v>50.941162040000002</v>
       </c>
       <c r="E97">
-        <v>-2.7248958220000001</v>
+        <v>-0.52488235000000005</v>
       </c>
       <c r="F97" s="4">
-        <v>877.64236615087304</v>
+        <v>1939.89</v>
       </c>
       <c r="G97">
-        <v>30095</v>
+        <v>30088</v>
       </c>
       <c r="H97">
-        <v>20075</v>
+        <v>20068</v>
       </c>
       <c r="I97" s="6">
-        <v>56.49</v>
+        <v>50.66</v>
       </c>
       <c r="J97" s="6">
-        <v>-2.1949722222222201</v>
+        <v>-0.2</v>
       </c>
       <c r="K97" t="s">
-        <v>61</v>
+        <v>57</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C636A33A-D890-486A-8AEE-7C63FD20A7FA}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="8"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="8">
+        <v>54.939653</v>
+      </c>
+      <c r="C2" s="8">
+        <v>4.9656729999999998</v>
+      </c>
+      <c r="D2">
+        <v>40000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="8">
+        <v>53.289901999999998</v>
+      </c>
+      <c r="C3" s="8">
+        <v>3.4488660000000002</v>
+      </c>
+      <c r="D3">
+        <v>40001</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="8">
+        <v>52.860048999999997</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2.9004590000000001</v>
+      </c>
+      <c r="D4">
+        <v>40002</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="8">
+        <v>57.140411</v>
+      </c>
+      <c r="C5" s="8">
+        <v>3.1467710000000002</v>
+      </c>
+      <c r="D5">
+        <v>40003</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="9">
+        <v>54.986789000000002</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2.0520510000000001</v>
+      </c>
+      <c r="D6">
+        <v>40004</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
